--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_VSC.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>77.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-5.5</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,11 @@
           <t>diff_casa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (12)</t>
+          <t>Q4 (8)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q2 (-7)</t>
+          <t>Q3 (-8.5)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,29 +701,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (12)</t>
+          <t>Diff médio casa: -16 | fora: 5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>resultado</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Diff médio em vitórias: 5 | em derrotas: -16</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>períodos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pior período: Q2 (-7)</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Melhor período: Q4 (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q3 (-8.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Drumwright sobe mais em vitórias (11 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -824,8 +864,41 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>71</v>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>71</v>
+      </c>
+      <c r="H3" t="n">
+        <v>87</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -836,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -924,60 +997,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. Stein</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>T. Simao</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-18</v>
+      </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>37.9</v>
       </c>
       <c r="F2" t="n">
         <v>17</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
         <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. Simao</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-15</v>
+      </c>
       <c r="E3" t="n">
         <v>37.9</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -985,9 +1086,15 @@
           <t>A. Guedes</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C4" t="n">
+        <v>7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
       <c r="E4" t="n">
         <v>39</v>
       </c>
@@ -1003,68 +1110,104 @@
       <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="n">
-        <v>37.9</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>15</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Runge</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>R. Stein</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-19</v>
+      </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1072,9 +1215,15 @@
           <t>R. Costa</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-4</v>
+      </c>
       <c r="E7" t="n">
         <v>5.2</v>
       </c>
@@ -1090,42 +1239,79 @@
       <c r="I7" t="n">
         <v>-3</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Costa</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>K. Warner</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="C8" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-16</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M. Houge</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-18</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M8"/>
+  <autoFilter ref="A1:M9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1231,25 +1417,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="H2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1274,25 +1460,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="H3" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="I3" t="n">
         <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K3" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="4">
@@ -1317,25 +1503,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>-17</v>
       </c>
       <c r="I4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J4" t="n">
-        <v>21</v>
+        <v>25.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>-8.5</v>
       </c>
     </row>
     <row r="5">
@@ -1360,25 +1546,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="H5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="J5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1393,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1505,164 +1691,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="n">
-        <v>4</v>
-      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="n">
         <v>2</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
@@ -1670,50 +1848,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
         <v>3</v>
       </c>
-      <c r="E5" t="n">
-        <v>12</v>
-      </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1725,99 +1903,209 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>D. Runge</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M. Drumwright</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>R. Costa</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q7"/>
+  <autoFilter ref="A1:Q9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1828,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1906,8 +2194,37 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922723</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_VSC.xlsx
@@ -18,11 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.3</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-10.0</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>-7.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (8)</t>
+          <t>Q4 (4.7)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q3 (-8.5)</t>
+          <t>Q3 (-7)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: -16 | fora: 5</t>
+          <t>Diff médio casa: -16 | fora: -7</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 5 | em derrotas: -16</t>
+          <t>Diff médio em vitórias: 5 | em derrotas: -17.5</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (8)</t>
+          <t>Melhor período: Q4 (4.7)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q3 (-8.5)</t>
+          <t>Pior período: Q3 (-7)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Drumwright sobe mais em vitórias (11 ppg).</t>
+          <t>A. Guedes sobe mais em vitórias (12.5 ppg).</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -839,66 +839,99 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>-19</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Away</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
+        <v>83</v>
+      </c>
+      <c r="E3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>83</v>
+      </c>
+      <c r="H3" t="n">
+        <v>78</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>71</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>87</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>-16</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>71</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>87</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>-16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I3"/>
+  <autoFilter ref="A1:I4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -997,173 +1030,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>26.2</v>
+        <v>16.5</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>-18</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>37.9</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-18</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>36.4</v>
+        <v>20.9</v>
       </c>
       <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15</v>
+      </c>
+      <c r="I3" t="n">
         <v>5</v>
       </c>
-      <c r="D3" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E3" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="F3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>-15</v>
+        <v>-3.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-11</v>
+        <v>-1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.5</v>
+        <v>26.2</v>
       </c>
       <c r="C4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
         <v>7</v>
-      </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>39</v>
-      </c>
-      <c r="F4" t="n">
-        <v>16</v>
-      </c>
-      <c r="G4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>-13</v>
       </c>
       <c r="L4" t="n">
-        <v>-9</v>
+        <v>-6.5</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.9</v>
+        <v>36.4</v>
       </c>
       <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" t="n">
         <v>6</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>40</v>
-      </c>
-      <c r="F5" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>15</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5</v>
-      </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L5" t="n">
-        <v>-9</v>
+        <v>-12.5</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -1182,13 +1215,13 @@
         <v>-19</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>38.8</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>-5.5</v>
       </c>
       <c r="H6" t="n">
         <v>17</v>
@@ -1197,117 +1230,127 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-19</v>
+        <v>-17.5</v>
       </c>
       <c r="L6" t="n">
         <v>-3</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.1</v>
+        <v>31.8</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>-4</v>
+        <v>-16</v>
       </c>
       <c r="E7" t="n">
-        <v>5.2</v>
+        <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>-3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-3</v>
-      </c>
+        <v>-15</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="K7" t="n">
-        <v>-4</v>
+        <v>-15.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.8</v>
+        <v>24.1</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-16</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>-18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-6</v>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>-12</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
       <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.1</v>
+        <v>3.1</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-23</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-18</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>-11.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1417,25 +1460,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="I2" t="n">
-        <v>17.5</v>
+        <v>15.7</v>
       </c>
       <c r="J2" t="n">
-        <v>17.5</v>
+        <v>18.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="3">
@@ -1460,22 +1503,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="H3" t="n">
-        <v>-10</v>
+        <v>-15</v>
       </c>
       <c r="I3" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="K3" t="n">
         <v>-5</v>
@@ -1503,25 +1546,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="H4" t="n">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="I4" t="n">
-        <v>17</v>
+        <v>18.7</v>
       </c>
       <c r="J4" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="5">
@@ -1546,25 +1589,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I5" t="n">
-        <v>25.5</v>
+        <v>23.7</v>
       </c>
       <c r="J5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>4.7</v>
       </c>
     </row>
   </sheetData>
@@ -1584,19 +1627,19 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1695,28 +1738,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>2</v>
-      </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1725,22 +1768,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1750,19 +1793,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
@@ -1771,31 +1814,31 @@
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -1808,93 +1851,101 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="C5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1903,163 +1954,163 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="C6" t="n">
-        <v>3.5</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.5</v>
-      </c>
       <c r="D8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E8" t="n">
-        <v>6.5</v>
+        <v>2.3</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2068,41 +2119,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. Costa</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>2</v>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1</v>
       </c>
-      <c r="O9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q9"/>
@@ -2116,11 +2175,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2223,8 +2282,37 @@
         <v>-16</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922728</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>72</v>
+      </c>
+      <c r="F4" t="n">
+        <v>91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-19</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_VSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_VSC.xlsx
@@ -18,11 +18,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>82.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-10.0</t>
+          <t>-7.0</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-16.0</t>
+          <t>-7.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q4 (4.7)</t>
+          <t>Q4 (3)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q3 (-7)</t>
+          <t>Q3 (-6.5)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: -16 | fora: -7</t>
+          <t>Diff médio casa: -7 | fora: -7</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 5 | em derrotas: -17.5</t>
+          <t>Diff médio em vitórias: 3.5 | em derrotas: -17.5</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q4 (4.7)</t>
+          <t>Melhor período: Q4 (3)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q3 (-7)</t>
+          <t>Pior período: Q3 (-6.5)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A. Guedes sobe mais em vitórias (12.5 ppg).</t>
+          <t>S. Verde sobe mais em vitórias (14 ppg).</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -930,8 +930,41 @@
         <v>-16</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>74</v>
+      </c>
+      <c r="H5" t="n">
+        <v>72</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I4"/>
+  <autoFilter ref="A1:I5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1030,173 +1063,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>S. Verde</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.5</v>
+        <v>18.4</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="E2" t="n">
-        <v>21</v>
+        <v>25.8</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>-23</v>
       </c>
       <c r="H2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>-11.5</v>
       </c>
       <c r="L2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. Runge</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="E3" t="n">
-        <v>24.6</v>
+        <v>33.8</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="H3" t="n">
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.5</v>
+        <v>-13</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.5</v>
+        <v>-3</v>
       </c>
       <c r="M3" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.2</v>
+        <v>17.9</v>
       </c>
       <c r="C4" t="n">
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>-18</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>33.8</v>
+        <v>21</v>
       </c>
       <c r="F4" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M4" t="n">
         <v>7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. Drumwright</t>
+          <t>D. Runge</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.4</v>
+        <v>20.1</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>-15</v>
+        <v>-3.5</v>
       </c>
       <c r="E5" t="n">
-        <v>33.3</v>
+        <v>24.6</v>
       </c>
       <c r="F5" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="G5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="L5" t="n">
         <v>-2.5</v>
       </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>12</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-13</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-12.5</v>
-      </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6">
@@ -1206,13 +1239,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>-19</v>
+        <v>-5.5</v>
       </c>
       <c r="E6" t="n">
         <v>38.8</v>
@@ -1224,10 +1257,10 @@
         <v>-5.5</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="J6" t="n">
         <v>15.5</v>
@@ -1236,122 +1269,140 @@
         <v>-17.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>M. Drumwright</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31.8</v>
+        <v>34</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>5.5</v>
       </c>
       <c r="D7" t="n">
-        <v>-16</v>
+        <v>-2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>39</v>
+        <v>33.3</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="G7" t="n">
-        <v>-15</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>-2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
       <c r="J7" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>-15.5</v>
+        <v>-13</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>-12</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. Houge</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.1</v>
+        <v>27.1</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>-18</v>
+        <v>1.5</v>
       </c>
       <c r="E8" t="n">
-        <v>21.9</v>
+        <v>39</v>
       </c>
       <c r="F8" t="n">
         <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>-6</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>-15</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-12</v>
+        <v>-15.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. Verde</t>
+          <t>M. Houge</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1</v>
+        <v>20.6</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="E9" t="n">
-        <v>25.8</v>
+        <v>21.9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
-        <v>-23</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+        <v>-6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-6</v>
+      </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-11.5</v>
+        <v>-12</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
+        <v>-5.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-11</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1460,25 +1511,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="H2" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="I2" t="n">
-        <v>15.7</v>
+        <v>17.8</v>
       </c>
       <c r="J2" t="n">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.7</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="3">
@@ -1503,25 +1554,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="G3" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="H3" t="n">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="I3" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="J3" t="n">
-        <v>22.3</v>
+        <v>20</v>
       </c>
       <c r="K3" t="n">
-        <v>-5</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="4">
@@ -1546,25 +1597,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="H4" t="n">
-        <v>-21</v>
+        <v>-26</v>
       </c>
       <c r="I4" t="n">
-        <v>18.7</v>
+        <v>17.8</v>
       </c>
       <c r="J4" t="n">
-        <v>25.7</v>
+        <v>24.2</v>
       </c>
       <c r="K4" t="n">
-        <v>-7</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="5">
@@ -1589,25 +1640,25 @@
         </is>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>87</v>
+      </c>
+      <c r="G5" t="n">
+        <v>75</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
-      </c>
-      <c r="F5" t="n">
-        <v>71</v>
-      </c>
-      <c r="G5" t="n">
-        <v>57</v>
-      </c>
-      <c r="H5" t="n">
-        <v>14</v>
-      </c>
-      <c r="I5" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>19</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.7</v>
       </c>
     </row>
   </sheetData>
@@ -1627,19 +1678,19 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
@@ -1734,111 +1785,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. Warner</t>
+          <t>R. Stein</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="C2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D2" t="n">
         <v>4.5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G2" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L2" t="n">
         <v>0.5</v>
       </c>
       <c r="M2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.5</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
         <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. Stein</t>
+          <t>K. Warner</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7</v>
+        <v>4.3</v>
       </c>
       <c r="C3" t="n">
-        <v>1.333333333333333</v>
+        <v>5.3</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>1.3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.7</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N3" t="n">
         <v>0.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="P3" t="n">
         <v>1.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -1848,25 +1899,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="E4" t="n">
         <v>3.5</v>
       </c>
       <c r="F4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -1875,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1887,10 +1938,10 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0.5</v>
@@ -1903,49 +1954,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="E5" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1954,111 +2005,111 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. Guedes</t>
+          <t>T. Simao</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.7</v>
       </c>
-      <c r="C6" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="D6" t="n">
-        <v>5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. Simao</t>
+          <t>A. Guedes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="C7" t="n">
-        <v>3.666666666666667</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.7</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="P7" t="n">
         <v>0.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2068,46 +2119,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -2123,44 +2174,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.7</v>
+      </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+      <c r="P9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>0.5</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2175,7 +2234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2311,8 +2370,37 @@
         <v>-19</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922734</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>74</v>
+      </c>
+      <c r="F5" t="n">
+        <v>72</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>